--- a/Database/260506_Datenbankdefinition.xlsx
+++ b/Database/260506_Datenbankdefinition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodelan\PycharmProjects\StustainabilityDrivenStructuralDesign\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99050E7-CB6D-46A5-970A-B83A130A43AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F04822-7AA6-4D26-BAD2-DD4C4385A65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="-9090" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="43080" yWindow="-8850" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="clarification" sheetId="5" r:id="rId1"/>
